--- a/docs/SuiteTD_organigramma_TD.xlsx
+++ b/docs/SuiteTD_organigramma_TD.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -529,13 +529,11 @@
           <t>Toscana Diagnostica</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>DIREZIONE</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Chief Executive Officer</t>
@@ -546,7 +544,6 @@
           <t>Epifani Francesco</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>SI</t>
@@ -564,13 +561,11 @@
           <t>Toscana Diagnostica</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>DIREZIONE</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Chief Operating Officer</t>
@@ -581,7 +576,6 @@
           <t>Zezza Valentina</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>NO</t>
@@ -599,13 +593,11 @@
           <t>Toscana Diagnostica</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>DIREZIONE</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Chief Financial Officer</t>
@@ -616,7 +608,6 @@
           <t>Malenchini Vincenzo</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>NO</t>
@@ -634,13 +625,11 @@
           <t>Toscana Diagnostica</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>DIREZIONE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Chief of Legal, People and Organization</t>
@@ -651,7 +640,6 @@
           <t>Corradi Angelica</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>NO</t>
@@ -669,13 +657,11 @@
           <t>Toscana Diagnostica</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>DIREZIONE</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Flow &amp; Back Office Management</t>
@@ -686,7 +672,6 @@
           <t>Greco Rosetta</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>NO</t>
@@ -704,13 +689,11 @@
           <t>Toscana Diagnostica</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>DIREZIONE</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Retail &amp; Communications Management</t>
@@ -721,7 +704,6 @@
           <t>Sansoni Silvia</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>NO</t>
@@ -739,13 +721,11 @@
           <t>Toscana Diagnostica</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>DIREZIONE</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>HSQ Management</t>
@@ -756,7 +736,6 @@
           <t>Cupelli Iacopo</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>NO</t>
@@ -784,7 +763,6 @@
           <t>AREA</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Responsabile di area</t>
@@ -795,7 +773,6 @@
           <t>Zezza Valentina</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>SI</t>
@@ -823,7 +800,6 @@
           <t>AREA</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Direttore Tecnico</t>
@@ -834,7 +810,6 @@
           <t>Balzano Maria Teresa</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>NO</t>
@@ -862,7 +837,6 @@
           <t>AREA</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -873,7 +847,6 @@
           <t>Taddei Gian Luigi</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>NO</t>
@@ -901,7 +874,6 @@
           <t>AREA</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Lab Operations Manager</t>
@@ -912,7 +884,6 @@
           <t>Arrighetti Sara</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>NO</t>
@@ -940,7 +911,6 @@
           <t>AREA</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Responsabile di area</t>
@@ -951,7 +921,6 @@
           <t>Sansoni Silvia</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>SI</t>
@@ -979,7 +948,6 @@
           <t>AREA</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Responsabile di area</t>
@@ -990,7 +958,6 @@
           <t>Epifani Francesco</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>SI</t>
@@ -1018,7 +985,6 @@
           <t>AREA</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Responsabile di area</t>
@@ -1029,7 +995,6 @@
           <t>Greco Rosetta</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>SI</t>
@@ -1057,7 +1022,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Site Manager</t>
@@ -1068,7 +1032,6 @@
           <t>De Marco Angela</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>SI</t>
@@ -1096,7 +1059,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -1107,7 +1069,6 @@
           <t>Saltarelli Oreste</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1135,7 +1096,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Site Manager</t>
@@ -1146,7 +1106,6 @@
           <t>Gabellini Riccardo</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>SI</t>
@@ -1174,7 +1133,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -1185,7 +1143,6 @@
           <t>Gastaldi Roberto</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1213,7 +1170,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -1224,7 +1180,6 @@
           <t>Chiaverini Alessandro</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1252,11 +1207,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>3</t>
@@ -1279,7 +1229,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -1290,7 +1239,6 @@
           <t>Chiaverini Alessandro</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1318,11 +1266,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>4</t>
@@ -1345,7 +1288,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -1356,7 +1298,6 @@
           <t>Chiaverini Alessandro</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1384,11 +1325,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>5</t>
@@ -1411,7 +1347,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Site Manager</t>
@@ -1422,7 +1357,6 @@
           <t>Mucci Piera</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>SI</t>
@@ -1450,7 +1384,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -1461,7 +1394,6 @@
           <t>Taddei Gian Luigi</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1489,7 +1421,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Site Manager</t>
@@ -1500,7 +1431,6 @@
           <t>Gelli Manuela</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>SI</t>
@@ -1528,7 +1458,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -1539,7 +1468,6 @@
           <t>Taddei Gian Luigi</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1567,7 +1495,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Site Manager</t>
@@ -1578,7 +1505,6 @@
           <t>Gucci Lorenzo</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>SI</t>
@@ -1606,7 +1532,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -1617,7 +1542,6 @@
           <t>Taddei Gian Luigi</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1645,7 +1569,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Site Manager</t>
@@ -1656,7 +1579,6 @@
           <t>Monti Milena</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>SI</t>
@@ -1684,7 +1606,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -1695,7 +1616,6 @@
           <t>Taddei Gian Luigi</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1723,7 +1643,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -1734,7 +1653,6 @@
           <t>Taddei Gian Luigi</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1762,11 +1680,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>5</t>
@@ -1789,7 +1702,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -1800,7 +1712,6 @@
           <t>Taddei Gian Luigi</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1828,11 +1739,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>6</t>
@@ -1855,7 +1761,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -1866,7 +1771,6 @@
           <t>Taddei Gian Luigi</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1894,11 +1798,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>7</t>
@@ -1921,7 +1820,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -1932,7 +1830,6 @@
           <t>Taddei Gian Luigi</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1960,11 +1857,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>8</t>
@@ -1987,7 +1879,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -1998,7 +1889,6 @@
           <t>Taddei Gian Luigi</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2026,11 +1916,6 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>9</t>
@@ -2053,7 +1938,6 @@
           <t>FUNZIONE</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Responsabile</t>
@@ -2064,7 +1948,6 @@
           <t>Greco Rosetta</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>SI</t>
@@ -2092,7 +1975,6 @@
           <t>FUNZIONE</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Responsabile</t>
@@ -2103,7 +1985,6 @@
           <t>Corradi Angelica</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>SI</t>
@@ -2131,7 +2012,6 @@
           <t>FUNZIONE</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Responsabile</t>
@@ -2142,7 +2022,6 @@
           <t>Cesati Valentina</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>SI</t>
@@ -2157,7 +2036,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Preanalitica</t>
+          <t>Laboratorio Sesto Fiorentino</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2167,18 +2046,18 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>REPARTO</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Responsabile di reparto</t>
+          <t>Direttore Tecnico</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arrighetti Sara</t>
+          <t>Balzano Maria Teresa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2196,7 +2075,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Core Lab</t>
+          <t>Laboratorio Sesto Fiorentino</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2206,41 +2085,41 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>REPARTO</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Responsabile di reparto</t>
+          <t>Direttore Sanitario</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Esposito Antonia</t>
+          <t>Taddei Gian Luigi</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Microbiologia</t>
+          <t>Preanalitica</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Laboratorio di Analisi</t>
+          <t>Laboratorio Sesto Fiorentino</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2248,7 +2127,6 @@
           <t>REPARTO</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Responsabile di reparto</t>
@@ -2256,10 +2134,9 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chilleri Chiara</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>Arrighetti Sara</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>SI</t>
@@ -2267,19 +2144,19 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Biologia Molecolare</t>
+          <t>Core Lab</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Laboratorio di Analisi</t>
+          <t>Laboratorio Sesto Fiorentino</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2287,7 +2164,6 @@
           <t>REPARTO</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>Responsabile di reparto</t>
@@ -2295,10 +2171,9 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Quattrone Silvia</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>Esposito Antonia</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>SI</t>
@@ -2306,19 +2181,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Anatomia Patologica</t>
+          <t>Microbiologia</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Laboratorio di Analisi</t>
+          <t>Laboratorio Sesto Fiorentino</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2326,7 +2201,6 @@
           <t>REPARTO</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Responsabile di reparto</t>
@@ -2334,10 +2208,9 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fondi Cristina</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>Chilleri Chiara</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>SI</t>
@@ -2345,44 +2218,116 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Biologia Molecolare</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Laboratorio Sesto Fiorentino</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>REPARTO</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Responsabile di reparto</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Quattrone Silvia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>Anatomia Patologica</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Laboratorio di Analisi</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Laboratorio Sesto Fiorentino</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
         <is>
           <t>REPARTO</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Responsabile di reparto</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Fondi Cristina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Anatomia Patologica</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Laboratorio Sesto Fiorentino</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>REPARTO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>Responsabile Tecnico</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Barelli Stefania</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>5</t>
         </is>

--- a/docs/SuiteTD_organigramma_TD.xlsx
+++ b/docs/SuiteTD_organigramma_TD.xlsx
@@ -2049,7 +2049,11 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>Direttore Tecnico</t>
@@ -2060,7 +2064,6 @@
           <t>Balzano Maria Teresa</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>SI</t>
@@ -2088,7 +2091,11 @@
           <t>SEDE</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
@@ -2099,7 +2106,6 @@
           <t>Taddei Gian Luigi</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2127,6 +2133,11 @@
           <t>REPARTO</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>Responsabile di reparto</t>
@@ -2164,6 +2175,11 @@
           <t>REPARTO</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>Responsabile di reparto</t>
@@ -2201,6 +2217,11 @@
           <t>REPARTO</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>Responsabile di reparto</t>
@@ -2238,6 +2259,11 @@
           <t>REPARTO</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>Responsabile di reparto</t>
@@ -2275,6 +2301,11 @@
           <t>REPARTO</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>Responsabile di reparto</t>
@@ -2310,6 +2341,11 @@
       <c r="C54" t="inlineStr">
         <is>
           <t>REPARTO</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LAB</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">

--- a/docs/SuiteTD_organigramma_TD.xlsx
+++ b/docs/SuiteTD_organigramma_TD.xlsx
@@ -462,18 +462,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="1">
@@ -489,35 +490,40 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>branch</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>site_code</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>person_email</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>is_head</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sort_order</t>
         </is>
@@ -531,25 +537,30 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>DIREZIONE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Epifani Francesco</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -558,199 +569,263 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Laboratorio di Analisi</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Toscana Diagnostica</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIREZIONE</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Chief Operating Officer</t>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AREA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Responsabile di area</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Zezza Valentina</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Toscana Diagnostica</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DIREZIONE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Chief Financial Officer</t>
-        </is>
-      </c>
+          <t>STAFF</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AREA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malenchini Vincenzo</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Zezza Valentina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Laboratorio di Analisi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Toscana Diagnostica</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DIREZIONE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Chief of Legal, People and Organization</t>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AREA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Corradi Angelica</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+          <t>Direttore Tecnico</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Balzano Maria Teresa</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Laboratorio di Analisi</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Toscana Diagnostica</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DIREZIONE</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Flow &amp; Back Office Management</t>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AREA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Greco Rosetta</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+          <t>Direttore Sanitario</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Taddei Gian Luigi</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Network Punti Prelievo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Toscana Diagnostica</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DIREZIONE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Retail &amp; Communications Management</t>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AREA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Responsabile di area</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>Sansoni Silvia</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Toscana Diagnostica</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DIREZIONE</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HSQ Management</t>
-        </is>
-      </c>
+          <t>STAFF</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AREA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cupelli Iacopo</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Malenchini Vincenzo</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Laboratorio di Analisi</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -760,34 +835,39 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>AREA</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Responsabile di area</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Zezza Valentina</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Epifani Francesco</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Laboratorio di Analisi</t>
+          <t>Legal, People and Organization</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -797,34 +877,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>STAFF</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>AREA</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Direttore Tecnico</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Balzano Maria Teresa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>Chief of Legal, People and Organization</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Corradi Angelica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Laboratorio di Analisi</t>
+          <t>Centri Polidiagnostici</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -834,34 +921,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>AREA</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Direttore Sanitario</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Taddei Gian Luigi</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Responsabile di area</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Greco Rosetta</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Laboratorio di Analisi</t>
+          <t>Flow &amp; Back Office Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -871,34 +963,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>STAFF</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>AREA</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Lab Operations Manager</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arrighetti Sara</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>Flow &amp; Back Office Manager</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Greco Rosetta</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Network Punti Prelievo</t>
+          <t>Retail &amp; Communications Management</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -908,34 +1007,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>STAFF</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>AREA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Responsabile di area</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
+          <t>Retail &amp; Communications Manager</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>Sansoni Silvia</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>HSQ Management</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -945,64 +1051,76 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>STAFF</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>AREA</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Responsabile di area</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Epifani Francesco</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+          <t>HSQ Manager</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cupelli Iacopo</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Centro Diagnostico Firenze CIFS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Centri Polidiagnostici</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Toscana Diagnostica</t>
-        </is>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AREA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Responsabile di area</t>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Greco Rosetta</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+          <t>Site Manager</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>De Marco Angela</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1019,25 +1137,30 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>De Marco Angela</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Direttore Sanitario</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Saltarelli Oreste</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1046,7 +1169,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Centro Diagnostico Firenze CIFS</t>
+          <t>Centro Medico Borgo San Lorenzo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1056,27 +1179,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Direttore Sanitario</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Saltarelli Oreste</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Site Manager</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Gabellini Riccardo</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1093,25 +1221,30 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gabellini Riccardo</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Direttore Sanitario</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Gastaldi Roberto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1120,7 +1253,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Centro Medico Borgo San Lorenzo</t>
+          <t>Centro Medico Livorno March</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1130,27 +1263,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Gastaldi Roberto</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chiaverini Alessandro</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1167,25 +1305,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Direttore Sanitario</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Chiaverini Alessandro</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1194,7 +1322,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Centro Medico Livorno March</t>
+          <t>Centro Medico Livorno Centro</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1204,12 +1332,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Direttore Sanitario</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chiaverini Alessandro</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1226,25 +1374,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Direttore Sanitario</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Chiaverini Alessandro</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1253,7 +1391,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Centro Medico Livorno Centro</t>
+          <t>Centro Medico Rosignano</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1263,12 +1401,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Direttore Sanitario</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chiaverini Alessandro</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1285,25 +1443,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Direttore Sanitario</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Chiaverini Alessandro</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1312,57 +1460,92 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Centro Medico Rosignano</t>
+          <t>Laboratorio Sesto Fiorentino</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Centri Polidiagnostici</t>
+          <t>Laboratorio di Analisi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Direttore Tecnico</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Balzano Maria Teresa</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Montemurlo</t>
+          <t>Laboratorio Sesto Fiorentino</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Network Punti Prelievo</t>
+          <t>Laboratorio di Analisi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Site Manager</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mucci Piera</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Direttore Sanitario</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Taddei Gian Luigi</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1381,25 +1564,30 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Direttore Sanitario</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Taddei Gian Luigi</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Site Manager</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Mucci Piera</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1408,7 +1596,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Calenzano</t>
+          <t>Montemurlo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1418,27 +1606,32 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gelli Manuela</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Direttore Sanitario</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Taddei Gian Luigi</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1455,25 +1648,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Direttore Sanitario</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Taddei Gian Luigi</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Site Manager</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Gelli Manuela</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1482,7 +1680,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Quarrata</t>
+          <t>Calenzano</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1492,27 +1690,32 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gucci Lorenzo</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Direttore Sanitario</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Taddei Gian Luigi</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1529,25 +1732,30 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Direttore Sanitario</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Taddei Gian Luigi</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Site Manager</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Gucci Lorenzo</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1556,7 +1764,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Livorno Labronica</t>
+          <t>Quarrata</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1566,27 +1774,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monti Milena</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Direttore Sanitario</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Taddei Gian Luigi</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1603,25 +1816,30 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Direttore Sanitario</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Taddei Gian Luigi</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Site Manager</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Monti Milena</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1630,7 +1848,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Livorno Carducci</t>
+          <t>Livorno Labronica</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1640,27 +1858,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Direttore Sanitario</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Taddei Gian Luigi</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1677,10 +1900,30 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Direttore Sanitario</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Taddei Gian Luigi</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1689,7 +1932,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Livorno Banditella</t>
+          <t>Livorno Carducci</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1699,27 +1942,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Direttore Sanitario</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Taddei Gian Luigi</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1736,10 +1969,30 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Direttore Sanitario</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Taddei Gian Luigi</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1748,7 +2001,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Livorno Picchianti</t>
+          <t>Livorno Banditella</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1758,27 +2011,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Direttore Sanitario</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Taddei Gian Luigi</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>7</t>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1795,10 +2038,30 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Direttore Sanitario</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Taddei Gian Luigi</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1807,7 +2070,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Livorno Centro</t>
+          <t>Livorno Picchianti</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1817,27 +2080,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Direttore Sanitario</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Taddei Gian Luigi</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1854,10 +2107,30 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Direttore Sanitario</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Taddei Gian Luigi</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1866,7 +2139,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Livorno Montenero</t>
+          <t>Livorno Centro</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1876,27 +2149,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Direttore Sanitario</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Taddei Gian Luigi</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1913,10 +2176,30 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>SEDE</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Direttore Sanitario</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Taddei Gian Luigi</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1925,44 +2208,34 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Service di Laboratorio</t>
+          <t>Livorno Montenero</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>Network Punti Prelievo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FUNZIONE</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Responsabile</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Greco Rosetta</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SEDE</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Medicina del Lavoro</t>
+          <t>Service di Laboratorio</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1972,34 +2245,39 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>FUNZIONE</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Responsabile</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Corradi Angelica</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Greco Rosetta</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Medicina del Lavoro</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2009,109 +2287,119 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>FUNZIONE</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Responsabile</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Cesati Valentina</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Corradi Angelica</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Laboratorio Sesto Fiorentino</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Laboratorio di Analisi</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>LINEA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LAB</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Direttore Tecnico</t>
+          <t>FUNZIONE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Balzano Maria Teresa</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
+          <t>Responsabile</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cesati Valentina</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>Preanalitica</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>Laboratorio Sesto Fiorentino</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Laboratorio di Analisi</t>
-        </is>
-      </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>LINEA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>REPARTO</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>LAB</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Direttore Sanitario</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Taddei Gian Luigi</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Responsabile di reparto</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Arrighetti Sara</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2120,7 +2408,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Preanalitica</t>
+          <t>Lab Operations Management</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2130,30 +2418,36 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>REPARTO</t>
+          <t>STAFF</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>FUNZIONE</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>LAB</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Responsabile di reparto</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>Lab Operations Manager</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>Arrighetti Sara</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2172,30 +2466,35 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>REPARTO</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>LAB</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Responsabile di reparto</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Esposito Antonia</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2214,30 +2513,35 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>REPARTO</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>LAB</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Responsabile di reparto</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Chilleri Chiara</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2256,30 +2560,35 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>REPARTO</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>LAB</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Responsabile di reparto</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Quattrone Silvia</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2298,30 +2607,35 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>REPARTO</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>LAB</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Responsabile di reparto</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Fondi Cristina</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2340,47 +2654,58 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>LINEA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>REPARTO</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>LAB</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Responsabile Tecnico</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Barelli Stefania</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="6">
     <dataValidation sqref="C10:C1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"LINEA,STAFF"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"LINEA,STAFF"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D10:D1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DIREZIONE,AREA,SEDE,REPARTO,FUNZIONE"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DIREZIONE,AREA,SEDE,REPARTO,FUNZIONE"</formula1>
     </dataValidation>
-    <dataValidation sqref="H10:H1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I10:I1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2395,7 +2720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2457,129 +2782,146 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>branch</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tipo</t>
+          <t>Collocazione</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DIREZIONE, AREA, SEDE, REPARTO, FUNZIONE. Predefinito: SEDE se c'è il codice sede, altrimenti AREA (REPARTO se l'unità superiore è una sede).</t>
+          <t>LINEA (pettine, aree operative) o STAFF (tecnostruttura: Finance, Legal People and Organization, HSQ...). Predefinito LINEA.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>site_code</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Codice sede</t>
+          <t>Tipo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Per i nodi SEDE (e i reparti): la sede dell'anagrafica.</t>
+          <t>DIREZIONE, AREA, SEDE, REPARTO, FUNZIONE. Predefinito: SEDE se c'è il codice sede, altrimenti AREA (REPARTO se l'unità superiore è una sede).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>site_code</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ruolo dell'incarico</t>
+          <t>Codice sede</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dal catalogo Ruoli (creato se manca): Chief Executive Officer, Site Manager, Direttore Sanitario, Responsabile...</t>
+          <t>Per i nodi SEDE (e i reparti): la sede dell'anagrafica.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Persona (Cognome Nome)</t>
+          <t>Ruolo dell'incarico</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chi ricopre l'incarico, come in Persone (cognome e nome). Vuota se la casella è ancora da assegnare (TBD).</t>
+          <t>Dal catalogo Ruoli (creato se manca): Chief Executive Officer, Site Manager, Direttore Sanitario, Responsabile...</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>person_email</t>
+          <t>person</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Email della persona</t>
+          <t>Persona (Cognome Nome)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>In alternativa al nome, l'email della persona in Persone.</t>
+          <t>Chi ricopre l'incarico, come in Persone (cognome e nome). Vuota se la casella è ancora da assegnare (TBD).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>is_head</t>
+          <t>person_email</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Responsabile</t>
+          <t>Email della persona</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SI se l'incarico è il responsabile dell'unità (la casella principale); NO per gli incarichi di staff e le altre figure (es. Direttore Sanitario).</t>
+          <t>In alternativa al nome, l'email della persona in Persone.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>is_head</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Responsabile</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SI se l'incarico è il responsabile dell'unità (la casella principale); NO per gli incarichi di staff e le altre figure (es. Direttore Sanitario).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>sort_order</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Ordine</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Numero per l'ordinamento dei nodi fratelli (facoltativo).</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Compila il foglio "Organigramma" lasciando la riga 1 (intestazioni) così com'è; la riga 2 è un esempio da sostituire o cancellare. Massimo 1000 righe per file. Le righe già presenti (stessa chiave) vengono aggiornate, non duplicate. Carica il file in Amministrazione &gt; Importazioni.</t>
         </is>
